--- a/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD93A938-8CE2-470D-97C1-1B35E8C03D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E8221C-274C-45B6-B542-9BEB752F4B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="171">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -599,15 +599,6 @@
     <t>TC1_ECP</t>
   </si>
   <si>
-    <t>Director1, Director2</t>
-  </si>
-  <si>
-    <t>TC3_ECP</t>
-  </si>
-  <si>
-    <t>Error message-Empty movie title</t>
-  </si>
-  <si>
     <t>TC5_ECP</t>
   </si>
   <si>
@@ -615,9 +606,6 @@
   </si>
   <si>
     <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
   </si>
   <si>
     <t>Statistics</t>
@@ -716,12 +704,135 @@
       <t xml:space="preserve"> modificareProdus(id,nume,pret,categorie,tip)</t>
     </r>
   </si>
+  <si>
+    <t>Nu se verifica cum trebuie limita superioara pentru pret</t>
+  </si>
+  <si>
+    <t>Acum se detecteaza si limita superioara</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Latte Nou</t>
+  </si>
+  <si>
+    <t>15,0</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Milk</t>
+  </si>
+  <si>
+    <t>produs actualizat fara exceptie</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>TC2_ECP</t>
+  </si>
+  <si>
+    <t>12,5</t>
+  </si>
+  <si>
+    <t>Simple</t>
+  </si>
+  <si>
+    <t>ValidationException cu mesaj Numele nu poate fi gol; produs nemodificat</t>
+  </si>
+  <si>
+    <t>Green Tea</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Orange Juice</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>Juice</t>
+  </si>
+  <si>
+    <t>Fresh</t>
+  </si>
+  <si>
+    <t>ValidationException cu mesaj Pret invalid; produs nemodificat</t>
+  </si>
+  <si>
+    <t>Bubble Tea</t>
+  </si>
+  <si>
+    <t>20,0</t>
+  </si>
+  <si>
+    <t>Boba</t>
+  </si>
+  <si>
+    <t>TC6_ECP</t>
+  </si>
+  <si>
+    <t>Iced Coffee</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (-)1,0</t>
+  </si>
+  <si>
+    <t>Cofee</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>TC7_BVA</t>
+  </si>
+  <si>
+    <t>Smoothie</t>
+  </si>
+  <si>
+    <t>Double.MAX_VALUE</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>TC8_BVA</t>
+  </si>
+  <si>
+    <t>Cappuccino</t>
+  </si>
+  <si>
+    <t>Math.nextUp(Double.MAX_VALUE)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -821,26 +932,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -851,14 +944,6 @@
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -940,8 +1025,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -984,8 +1102,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBD4B4"/>
+        <bgColor rgb="FFFBD4B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1022,16 +1152,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1041,34 +1167,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1171,80 +1273,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1263,17 +1291,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -1404,6 +1421,219 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="double">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="double">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="double">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1411,7 +1641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1421,365 +1651,390 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2093,24 +2348,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69"/>
-      <c r="H1" s="51" t="s">
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="41"/>
+      <c r="H1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="83" t="s">
+      <c r="H2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
@@ -2118,7 +2373,7 @@
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -2127,7 +2382,7 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -2136,11 +2391,11 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="37"/>
+      <c r="B6" s="24"/>
       <c r="H6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2149,7 +2404,7 @@
     </row>
     <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="35" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2198,7 +2453,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2210,7 +2465,7 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="35" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2220,13 +2475,13 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="47" t="s">
-        <v>131</v>
+      <c r="C20" s="33" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -2264,25 +2519,25 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="48"/>
-      <c r="B24" s="82" t="s">
+      <c r="A24" s="34"/>
+      <c r="B24" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="82"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="82"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="50"/>
+      <c r="C26" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2319,124 +2574,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="75"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="G5" s="77" t="s">
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="G5" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="61" t="s">
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="61"/>
+      <c r="Q6" s="67"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="43" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="23" t="s">
+      <c r="G7" s="52"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="57" t="s">
+      <c r="N7" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="58"/>
-      <c r="P7" s="57" t="s">
+      <c r="O7" s="64"/>
+      <c r="P7" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" s="58"/>
+      <c r="Q7" s="64"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="70"/>
+      <c r="C8" s="43"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="17">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2457,29 +2712,29 @@
       <c r="M8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N8" s="53" t="s">
+      <c r="N8" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="O8" s="54" t="s">
+      <c r="O8" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="P8" s="53" t="s">
+      <c r="P8" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="54"/>
+      <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="43" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="23">
+      <c r="G9" s="17">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -2500,324 +2755,324 @@
       <c r="M9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N9" s="53" t="s">
+      <c r="N9" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="O9" s="54" t="s">
+      <c r="O9" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="P9" s="53" t="s">
+      <c r="P9" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="Q9" s="54"/>
+      <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="43"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="23">
         <v>3</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="9">
         <v>2012</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="65" t="s">
+      <c r="N10" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="O10" s="66"/>
-      <c r="P10" s="65" t="s">
+      <c r="O10" s="56"/>
+      <c r="P10" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="66"/>
+      <c r="Q10" s="56"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="43" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="36">
+      <c r="G11" s="23">
         <v>4</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="65" t="s">
+      <c r="N11" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="O11" s="66"/>
-      <c r="P11" s="65" t="s">
+      <c r="O11" s="56"/>
+      <c r="P11" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="66"/>
+      <c r="Q11" s="56"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="70"/>
+      <c r="C12" s="43"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="8">
         <v>5</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="63" t="s">
+      <c r="O12" s="6"/>
+      <c r="P12" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="Q12" s="64"/>
+      <c r="Q12" s="58"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="44" t="s">
         <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="G13" s="13">
+      <c r="G13" s="8">
         <v>6</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="N13" s="63" t="s">
+      <c r="N13" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="O13" s="64"/>
-      <c r="P13" s="63" t="s">
+      <c r="O13" s="58"/>
+      <c r="P13" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="Q13" s="64"/>
+      <c r="Q13" s="58"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="72"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="13">
         <v>7</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="12">
         <v>10</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="M14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="80" t="s">
+      <c r="N14" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="O14" s="81"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="56"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="60"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="43" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="G15" s="19">
+      <c r="G15" s="13">
         <v>8</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="56"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="70"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="56"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="43" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="56"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="62"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="60"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="70"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="56"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="60"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="43" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="G19" s="23"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="56"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="60"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -2825,11 +3080,36 @@
       <c r="D22" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -2846,31 +3126,6 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2903,44 +3158,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="75"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="77" t="s">
+      <c r="G5" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
     </row>
     <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -2952,608 +3207,632 @@
       <c r="D6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="7"/>
+      <c r="G6" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="78" t="s">
+      <c r="H6" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="78" t="s">
+      <c r="I6" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="K6" s="86" t="s">
+      <c r="K6" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="86" t="s">
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="78"/>
+      <c r="Q6" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="R6" s="88"/>
+      <c r="R6" s="78"/>
     </row>
     <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="71">
+      <c r="B7" s="44">
         <v>1</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="71" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="23" t="s">
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="35" t="s">
+      <c r="M7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="35" t="s">
+      <c r="N7" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="O7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="P7" s="23" t="s">
+      <c r="P7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" s="57" t="s">
+      <c r="Q7" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="R7" s="58"/>
+      <c r="R7" s="64"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="91"/>
-      <c r="C8" s="93"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="17">
         <v>1</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="11">
         <v>1</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="85"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="79"/>
+      <c r="R8" s="80"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="91"/>
-      <c r="C9" s="93"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="13">
         <v>2</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="14">
         <v>2</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21" t="s">
+      <c r="I9" s="15"/>
+      <c r="J9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="22" t="s">
+      <c r="K9" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18" t="s">
+      <c r="N9" s="12"/>
+      <c r="O9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="P9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Q9" s="63" t="s">
+      <c r="Q9" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="R9" s="64"/>
+      <c r="R9" s="58"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="91"/>
-      <c r="C10" s="93"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="72"/>
       <c r="D10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="17">
         <v>3</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="11">
         <v>3</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="33" t="s">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="L10" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="21">
         <v>2010</v>
       </c>
-      <c r="N10" s="34" t="s">
+      <c r="N10" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="O10" s="34" t="s">
+      <c r="O10" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="P10" s="34" t="s">
+      <c r="P10" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="84" t="s">
+      <c r="Q10" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="R10" s="85"/>
+      <c r="R10" s="80"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="91"/>
-      <c r="C11" s="93"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="72"/>
       <c r="D11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="17">
         <v>4</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="11">
         <v>4</v>
       </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="33" t="s">
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="34" t="s">
+      <c r="L11" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="21">
         <v>2010</v>
       </c>
-      <c r="N11" s="34" t="s">
+      <c r="N11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="O11" s="34" t="s">
+      <c r="O11" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="34" t="s">
+      <c r="P11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="Q11" s="84" t="s">
+      <c r="Q11" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="R11" s="85"/>
+      <c r="R11" s="80"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="72"/>
-      <c r="C12" s="94"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="73"/>
       <c r="D12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="17">
         <v>5</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="11">
         <v>5</v>
       </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="33" t="s">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="21">
         <v>2010</v>
       </c>
-      <c r="N12" s="34" t="s">
+      <c r="N12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="O12" s="34" t="s">
+      <c r="O12" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="P12" s="34" t="s">
+      <c r="P12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="Q12" s="84" t="s">
+      <c r="Q12" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="R12" s="85"/>
+      <c r="R12" s="80"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="71">
+      <c r="B13" s="44">
         <v>2</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="44" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="13">
         <v>6</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="14">
         <v>6</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21" t="s">
+      <c r="I13" s="15"/>
+      <c r="J13" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="12">
         <v>2010</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="O13" s="18" t="s">
+      <c r="O13" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="P13" s="18" t="s">
+      <c r="P13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="63" t="s">
+      <c r="Q13" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="R13" s="64"/>
+      <c r="R13" s="58"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
       <c r="D14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="17">
         <v>7</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="11">
         <v>7</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="84"/>
-      <c r="R14" s="85"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="79"/>
+      <c r="R14" s="80"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="91"/>
-      <c r="C15" s="91"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
       <c r="D15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="17">
         <v>8</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="11">
         <v>8</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="85"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="79"/>
+      <c r="R15" s="80"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="91"/>
-      <c r="C16" s="91"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="17">
         <v>9</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="85"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="79"/>
+      <c r="R16" s="80"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="17">
         <v>10</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="85"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="79"/>
+      <c r="R17" s="80"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
       <c r="D18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="17">
         <v>11</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="85"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="80"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="71">
+      <c r="B19" s="44">
         <v>3</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="71" t="s">
         <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="17">
         <v>12</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="85"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="80"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="91"/>
-      <c r="C20" s="93"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="72"/>
       <c r="D20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="17">
         <v>13</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="85"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="79"/>
+      <c r="R20" s="80"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="91"/>
-      <c r="C21" s="93"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="72"/>
       <c r="D21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="17">
         <v>14</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="85"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="80"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="91"/>
-      <c r="C22" s="93"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="72"/>
       <c r="D22" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="17">
         <v>15</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="85"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="79"/>
+      <c r="R22" s="80"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="91"/>
-      <c r="C23" s="93"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="72"/>
       <c r="D23" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="17">
         <v>16</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="84"/>
-      <c r="R23" s="85"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="79"/>
+      <c r="R23" s="80"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="72"/>
-      <c r="C24" s="94"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="73"/>
       <c r="D24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="17">
         <v>17</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="84"/>
-      <c r="R24" s="85"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="79"/>
+      <c r="R24" s="80"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="71">
+      <c r="B25" s="44">
         <v>4</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="71" t="s">
         <v>47</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="17">
         <v>18</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="85"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="79"/>
+      <c r="R25" s="80"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="91"/>
-      <c r="C26" s="93"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="72"/>
       <c r="D26" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="91"/>
-      <c r="C27" s="93"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="91"/>
-      <c r="C28" s="93"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="72"/>
       <c r="D28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="43"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="75"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="30"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="91"/>
-      <c r="C29" s="93"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="95"/>
-      <c r="N29" s="44"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="31"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="72"/>
-      <c r="C30" s="94"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="73"/>
       <c r="D30" s="2" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3570,30 +3849,6 @@
     <mergeCell ref="G5:R5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3609,564 +3864,525 @@
   <dimension ref="B1:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+    <col min="11" max="11" width="71.28515625" customWidth="1"/>
+    <col min="12" max="12" width="53.85546875" customWidth="1"/>
     <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="134" t="s">
+      <c r="B3" s="82" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="134"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="78" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+    </row>
+    <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="128" t="s">
+      <c r="C4" s="104" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="61" t="s">
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="61"/>
+      <c r="L4" s="110"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="107"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="122"/>
-      <c r="M5" s="26" t="s">
+      <c r="B5" s="111"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="114" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="114" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="114" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="114" t="s">
+        <v>135</v>
+      </c>
+      <c r="J5" s="114" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="L5" s="115" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24">
+    <row r="6" spans="2:14" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="116">
         <v>1</v>
       </c>
-      <c r="C6" s="105" t="s">
+      <c r="C6" s="117" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="116" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="29">
-        <v>2010</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" s="123" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="124" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="12">
+      <c r="F6" s="119">
+        <v>10</v>
+      </c>
+      <c r="G6" s="120" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" s="120" t="s">
+        <v>138</v>
+      </c>
+      <c r="I6" s="120" t="s">
+        <v>139</v>
+      </c>
+      <c r="J6" s="121" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="L6" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="115">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="105"/>
-      <c r="D7" s="31" t="s">
+      <c r="C7" s="123"/>
+      <c r="D7" s="124" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="115" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="125">
+        <v>11</v>
+      </c>
+      <c r="G7" s="126" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="126" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="126" t="s">
+        <v>139</v>
+      </c>
+      <c r="J7" s="127" t="s">
+        <v>145</v>
+      </c>
+      <c r="K7" s="128" t="s">
+        <v>146</v>
+      </c>
+      <c r="L7" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="115">
+        <v>3</v>
+      </c>
+      <c r="C8" s="123"/>
+      <c r="D8" s="124" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="F8" s="125">
+        <v>12</v>
+      </c>
+      <c r="G8" s="126" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="126" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="126" t="s">
+        <v>149</v>
+      </c>
+      <c r="J8" s="127" t="s">
+        <v>150</v>
+      </c>
+      <c r="K8" s="129" t="s">
+        <v>141</v>
+      </c>
+      <c r="L8" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="115">
+        <v>4</v>
+      </c>
+      <c r="C9" s="123"/>
+      <c r="D9" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="E9" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="125">
+        <v>13</v>
+      </c>
+      <c r="G9" s="126" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" s="126" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="126" t="s">
+        <v>153</v>
+      </c>
+      <c r="J9" s="127" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" s="128" t="s">
+        <v>155</v>
+      </c>
+      <c r="L9" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="115">
+        <v>5</v>
+      </c>
+      <c r="C10" s="123"/>
+      <c r="D10" s="118" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="8">
-        <v>2010</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7" s="130" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="131"/>
-      <c r="M7" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="12">
-        <f t="shared" ref="B8:B13" si="0">B7+1</f>
-        <v>3</v>
-      </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="31" t="s">
+      <c r="E10" s="115" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="115">
+        <v>14</v>
+      </c>
+      <c r="G10" s="116" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" s="116" t="s">
+        <v>157</v>
+      </c>
+      <c r="I10" s="116" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="115" t="s">
+        <v>158</v>
+      </c>
+      <c r="K10" s="130" t="s">
+        <v>141</v>
+      </c>
+      <c r="L10" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="115">
+        <f>B10+1</f>
+        <v>6</v>
+      </c>
+      <c r="C11" s="123"/>
+      <c r="D11" s="118" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="115" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="131">
+        <v>15</v>
+      </c>
+      <c r="G11" s="131" t="s">
+        <v>160</v>
+      </c>
+      <c r="H11" s="131" t="s">
+        <v>161</v>
+      </c>
+      <c r="I11" s="131" t="s">
+        <v>162</v>
+      </c>
+      <c r="J11" s="131" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" s="128" t="s">
+        <v>155</v>
+      </c>
+      <c r="L11" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="115">
+        <f>B11+1</f>
+        <v>7</v>
+      </c>
+      <c r="C12" s="123"/>
+      <c r="D12" s="124" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="131">
+        <v>16</v>
+      </c>
+      <c r="G12" s="132" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="132" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="131" t="s">
+        <v>163</v>
+      </c>
+      <c r="J12" s="131" t="s">
+        <v>167</v>
+      </c>
+      <c r="K12" s="133" t="s">
+        <v>141</v>
+      </c>
+      <c r="L12" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="114">
+        <v>8</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="134" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="115" t="s">
+        <v>168</v>
+      </c>
+      <c r="F13" s="135">
+        <v>17</v>
+      </c>
+      <c r="G13" s="136" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="137" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" s="114" t="s">
+        <v>162</v>
+      </c>
+      <c r="J13" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="138" t="s">
+        <v>155</v>
+      </c>
+      <c r="L13" s="116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+    </row>
+    <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="12">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C9" s="105"/>
-      <c r="D9" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="132" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="133"/>
-      <c r="M9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10" s="125" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="126"/>
-      <c r="M10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C11" s="105"/>
-      <c r="D11" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="12" t="s">
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="K11" s="125" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" s="126"/>
-      <c r="M11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="12">
-        <f t="shared" si="0"/>
+      <c r="H17" s="90" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="93"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="92"/>
+      <c r="M17" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="N17" s="93"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="92"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="86" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="87" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="89" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="95"/>
+      <c r="J18" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="M18" s="99" t="s">
+        <v>122</v>
+      </c>
+      <c r="N18" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="O18" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="P18" s="89" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="86"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="89"/>
+    </row>
+    <row r="20" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B20" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="25">
+        <v>8</v>
+      </c>
+      <c r="D20" s="27">
         <v>7</v>
       </c>
-      <c r="C12" s="105"/>
-      <c r="D12" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="125" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="126"/>
-      <c r="M12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25">
-        <f t="shared" si="0"/>
+      <c r="E20" s="27">
+        <v>1</v>
+      </c>
+      <c r="F20" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="101" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="I20" s="85"/>
+      <c r="J20" s="2">
         <v>8</v>
       </c>
-      <c r="C13" s="106"/>
-      <c r="D13" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="119" t="s">
-        <v>47</v>
-      </c>
-      <c r="L13" s="120"/>
-      <c r="M13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-    </row>
-    <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="98" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="98" t="s">
-        <v>120</v>
-      </c>
-      <c r="N17" s="99"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="101"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="112" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="113" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" s="97" t="s">
+      <c r="K20" s="27">
+        <v>8</v>
+      </c>
+      <c r="L20" s="28">
+        <v>0</v>
+      </c>
+      <c r="M20" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="96" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="118" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="114" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="115"/>
-      <c r="J18" s="97" t="s">
-        <v>121</v>
-      </c>
-      <c r="K18" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="L18" s="96" t="s">
-        <v>123</v>
-      </c>
-      <c r="M18" s="102" t="s">
-        <v>126</v>
-      </c>
-      <c r="N18" s="97" t="s">
-        <v>121</v>
-      </c>
-      <c r="O18" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="P18" s="96" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="112"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="96"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="96"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="38">
+      <c r="N20" s="2">
         <v>8</v>
       </c>
-      <c r="D20" s="40">
-        <v>5</v>
-      </c>
-      <c r="E20" s="40">
-        <v>3</v>
-      </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="110" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" s="111"/>
-      <c r="J20" s="2">
-        <v>3</v>
-      </c>
-      <c r="K20" s="40">
-        <v>3</v>
-      </c>
-      <c r="L20" s="41">
-        <v>0</v>
-      </c>
-      <c r="M20" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="N20" s="2">
-        <v>5</v>
-      </c>
-      <c r="O20" s="40">
-        <v>5</v>
-      </c>
-      <c r="P20" s="41">
+      <c r="O20" s="27">
+        <v>8</v>
+      </c>
+      <c r="P20" s="28">
         <v>0</v>
       </c>
     </row>
@@ -4174,21 +4390,13 @@
       <c r="M21" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
+  <mergeCells count="28">
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
@@ -4205,13 +4413,18 @@
     <mergeCell ref="H18:I19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:L4"/>
   </mergeCells>
+  <conditionalFormatting sqref="F4:L4">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(F4))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4219,21 +4432,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4371,24 +4569,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4404,4 +4600,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E8221C-274C-45B6-B542-9BEB752F4B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD93A938-8CE2-470D-97C1-1B35E8C03D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="134">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -599,6 +599,15 @@
     <t>TC1_ECP</t>
   </si>
   <si>
+    <t>Director1, Director2</t>
+  </si>
+  <si>
+    <t>TC3_ECP</t>
+  </si>
+  <si>
+    <t>Error message-Empty movie title</t>
+  </si>
+  <si>
     <t>TC5_ECP</t>
   </si>
   <si>
@@ -606,6 +615,9 @@
   </si>
   <si>
     <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>TC5_BVA</t>
   </si>
   <si>
     <t>Statistics</t>
@@ -704,135 +716,12 @@
       <t xml:space="preserve"> modificareProdus(id,nume,pret,categorie,tip)</t>
     </r>
   </si>
-  <si>
-    <t>Nu se verifica cum trebuie limita superioara pentru pret</t>
-  </si>
-  <si>
-    <t>Acum se detecteaza si limita superioara</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Latte Nou</t>
-  </si>
-  <si>
-    <t>15,0</t>
-  </si>
-  <si>
-    <t>Coffee</t>
-  </si>
-  <si>
-    <t>Milk</t>
-  </si>
-  <si>
-    <t>produs actualizat fara exceptie</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>TC2_ECP</t>
-  </si>
-  <si>
-    <t>12,5</t>
-  </si>
-  <si>
-    <t>Simple</t>
-  </si>
-  <si>
-    <t>ValidationException cu mesaj Numele nu poate fi gol; produs nemodificat</t>
-  </si>
-  <si>
-    <t>Green Tea</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>Tea</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Orange Juice</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>Juice</t>
-  </si>
-  <si>
-    <t>Fresh</t>
-  </si>
-  <si>
-    <t>ValidationException cu mesaj Pret invalid; produs nemodificat</t>
-  </si>
-  <si>
-    <t>Bubble Tea</t>
-  </si>
-  <si>
-    <t>20,0</t>
-  </si>
-  <si>
-    <t>Boba</t>
-  </si>
-  <si>
-    <t>TC6_ECP</t>
-  </si>
-  <si>
-    <t>Iced Coffee</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (-)1,0</t>
-  </si>
-  <si>
-    <t>Cofee</t>
-  </si>
-  <si>
-    <t>Cold</t>
-  </si>
-  <si>
-    <t>TC7_BVA</t>
-  </si>
-  <si>
-    <t>Smoothie</t>
-  </si>
-  <si>
-    <t>Double.MAX_VALUE</t>
-  </si>
-  <si>
-    <t>Fruit</t>
-  </si>
-  <si>
-    <t>TC8_BVA</t>
-  </si>
-  <si>
-    <t>Cappuccino</t>
-  </si>
-  <si>
-    <t>Math.nextUp(Double.MAX_VALUE)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -932,8 +821,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -944,6 +851,14 @@
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1025,41 +940,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1102,20 +984,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBD4B4"/>
-        <bgColor rgb="FFFBD4B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="41">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1152,12 +1022,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1167,10 +1041,34 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1273,6 +1171,80 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1291,6 +1263,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -1421,219 +1404,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1641,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1651,23 +1421,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1682,359 +1462,324 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2348,24 +2093,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="41"/>
-      <c r="H1" s="37" t="s">
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="69"/>
+      <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
@@ -2373,7 +2118,7 @@
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -2382,7 +2127,7 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -2391,11 +2136,11 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="24"/>
+      <c r="B6" s="37"/>
       <c r="H6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2404,7 +2149,7 @@
     </row>
     <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="49" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2453,7 +2198,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2465,7 +2210,7 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="49" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2475,13 +2220,13 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="33" t="s">
-        <v>127</v>
+      <c r="C20" s="47" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -2519,25 +2264,25 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="38" t="s">
+      <c r="A24" s="48"/>
+      <c r="B24" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="82"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="36"/>
+      <c r="C26" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2574,124 +2319,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="G5" s="50" t="s">
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="G5" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="65" t="s">
+      <c r="H6" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="63" t="s">
+      <c r="I6" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="67" t="s">
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="67"/>
+      <c r="Q6" s="61"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="70" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="17" t="s">
+      <c r="G7" s="79"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="N7" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="64"/>
-      <c r="P7" s="63" t="s">
+      <c r="O7" s="58"/>
+      <c r="P7" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" s="64"/>
+      <c r="Q7" s="58"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="43"/>
+      <c r="C8" s="70"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="23">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2712,29 +2457,29 @@
       <c r="M8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N8" s="61" t="s">
+      <c r="N8" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="O8" s="62" t="s">
+      <c r="O8" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="P8" s="61" t="s">
+      <c r="P8" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="62"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="70" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="17">
+      <c r="G9" s="23">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -2755,324 +2500,324 @@
       <c r="M9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N9" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="O9" s="62" t="s">
+      <c r="N9" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="P9" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q9" s="62"/>
+      <c r="P9" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="43"/>
+      <c r="C10" s="70"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="36">
         <v>3</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="14">
         <v>2012</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="55" t="s">
+      <c r="N10" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="O10" s="56"/>
-      <c r="P10" s="55" t="s">
+      <c r="O10" s="66"/>
+      <c r="P10" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="56"/>
+      <c r="Q10" s="66"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="70" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="23">
+      <c r="G11" s="36">
         <v>4</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="9" t="s">
+      <c r="H11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="O11" s="56"/>
-      <c r="P11" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q11" s="56"/>
+      <c r="M11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" s="66"/>
+      <c r="P11" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q11" s="66"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="43"/>
+      <c r="C12" s="70"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="13">
         <v>5</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="57" t="s">
+      <c r="O12" s="9"/>
+      <c r="P12" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="Q12" s="58"/>
+      <c r="Q12" s="64"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="71" t="s">
         <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="G13" s="8">
+      <c r="G13" s="13">
         <v>6</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="L13" s="6" t="s">
+      <c r="H13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="O13" s="58"/>
-      <c r="P13" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q13" s="58"/>
+      <c r="M13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N13" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="64"/>
+      <c r="P13" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q13" s="64"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="45"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="19">
         <v>7</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="18">
         <v>10</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="53" t="s">
+      <c r="N14" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="O14" s="54"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="60"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="55"/>
+      <c r="Q14" s="56"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="70" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="G15" s="13">
+      <c r="G15" s="19">
         <v>8</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="60"/>
+      <c r="H15" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="55"/>
+      <c r="Q15" s="56"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="43"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="60"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="56"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="70" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="60"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="56"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="43"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="60"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="56"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="70" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="G19" s="17"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="60"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="55"/>
+      <c r="Q19" s="56"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="43"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -3080,36 +2825,11 @@
       <c r="D22" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -3126,6 +2846,31 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3158,44 +2903,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
     </row>
     <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -3207,616 +2952,624 @@
       <c r="D6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="G6" s="51" t="s">
+      <c r="E6" s="10"/>
+      <c r="G6" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="65" t="s">
+      <c r="J6" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="K6" s="77" t="s">
+      <c r="K6" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="77" t="s">
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="R6" s="78"/>
+      <c r="R6" s="88"/>
     </row>
     <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="44">
+      <c r="B7" s="71">
         <v>1</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="92" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="17" t="s">
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="17" t="s">
+      <c r="O7" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="P7" s="17" t="s">
+      <c r="P7" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" s="63" t="s">
+      <c r="Q7" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="R7" s="64"/>
+      <c r="R7" s="58"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="70"/>
-      <c r="C8" s="72"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="23">
         <v>1</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="17">
         <v>1</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="79"/>
-      <c r="R8" s="80"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="85"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="70"/>
-      <c r="C9" s="72"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="19">
         <v>2</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="20">
         <v>2</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15" t="s">
+      <c r="I9" s="21"/>
+      <c r="J9" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q9" s="57" t="s">
+      <c r="L9" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="R9" s="58"/>
+      <c r="R9" s="64"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="70"/>
-      <c r="C10" s="72"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="23">
         <v>3</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="17">
         <v>3</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="20" t="s">
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="34">
         <v>2010</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="N10" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="O10" s="21" t="s">
+      <c r="O10" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="P10" s="21" t="s">
+      <c r="P10" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="79" t="s">
+      <c r="Q10" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="R10" s="80"/>
+      <c r="R10" s="85"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="70"/>
-      <c r="C11" s="72"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="23">
         <v>4</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="17">
         <v>4</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="20" t="s">
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11" s="34">
         <v>2010</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="O11" s="21" t="s">
+      <c r="O11" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="21" t="s">
+      <c r="P11" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="Q11" s="79" t="s">
+      <c r="Q11" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="R11" s="80"/>
+      <c r="R11" s="85"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="45"/>
-      <c r="C12" s="73"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="94"/>
       <c r="D12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="23">
         <v>5</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="17">
         <v>5</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="20" t="s">
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="34">
         <v>2010</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="O12" s="21" t="s">
+      <c r="O12" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="P12" s="21" t="s">
+      <c r="P12" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="Q12" s="79" t="s">
+      <c r="Q12" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="R12" s="80"/>
+      <c r="R12" s="85"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="44">
+      <c r="B13" s="71">
         <v>2</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="71" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="19">
         <v>6</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="20">
         <v>6</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15" t="s">
+      <c r="I13" s="21"/>
+      <c r="J13" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="18">
         <v>2010</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="57" t="s">
+      <c r="Q13" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="R13" s="58"/>
+      <c r="R13" s="64"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="91"/>
       <c r="D14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="23">
         <v>7</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="17">
         <v>7</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="79"/>
-      <c r="R14" s="80"/>
+      <c r="I14" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="85"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="91"/>
       <c r="D15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="23">
         <v>8</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="17">
         <v>8</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="79"/>
-      <c r="R15" s="80"/>
+      <c r="I15" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
       <c r="D16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="23">
         <v>9</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="80"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="85"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
       <c r="D17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="23">
         <v>10</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="79"/>
-      <c r="R17" s="80"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="85"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
       <c r="D18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="23">
         <v>11</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="79"/>
-      <c r="R18" s="80"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="85"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="44">
+      <c r="B19" s="71">
         <v>3</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="92" t="s">
         <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="23">
         <v>12</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="80"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="85"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="70"/>
-      <c r="C20" s="72"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="23">
         <v>13</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="80"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="85"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="70"/>
-      <c r="C21" s="72"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="23">
         <v>14</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="79"/>
-      <c r="R21" s="80"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="85"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="70"/>
-      <c r="C22" s="72"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="23">
         <v>15</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="79"/>
-      <c r="R22" s="80"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="85"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="70"/>
-      <c r="C23" s="72"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="23">
         <v>16</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="79"/>
-      <c r="R23" s="80"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="85"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="45"/>
-      <c r="C24" s="73"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="94"/>
       <c r="D24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="23">
         <v>17</v>
       </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="79"/>
-      <c r="R24" s="80"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="84"/>
+      <c r="R24" s="85"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="44">
+      <c r="B25" s="71">
         <v>4</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="92" t="s">
         <v>47</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="23">
         <v>18</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="79"/>
-      <c r="R25" s="80"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="85"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="70"/>
-      <c r="C26" s="72"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="70"/>
-      <c r="C27" s="72"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="93"/>
       <c r="D27" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="70"/>
-      <c r="C28" s="72"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
-      <c r="K28" s="75"/>
-      <c r="L28" s="75"/>
-      <c r="M28" s="75"/>
-      <c r="N28" s="30"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="89"/>
+      <c r="N28" s="43"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="70"/>
-      <c r="C29" s="72"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="93"/>
       <c r="D29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="31"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="44"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="45"/>
-      <c r="C30" s="73"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="94"/>
       <c r="D30" s="2" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
@@ -3833,22 +3586,14 @@
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:R5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3864,525 +3609,564 @@
   <dimension ref="B1:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="71.28515625" customWidth="1"/>
-    <col min="12" max="12" width="53.85546875" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" customWidth="1"/>
     <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="134" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-    </row>
-    <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="103" t="s">
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="134"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="128" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="105" t="s">
+      <c r="D4" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="106" t="s">
+      <c r="E4" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="107" t="s">
+      <c r="F4" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109" t="s">
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="110"/>
+      <c r="N4" s="61"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="111"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="114" t="s">
-        <v>132</v>
-      </c>
-      <c r="G5" s="114" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="114" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" s="114" t="s">
-        <v>135</v>
-      </c>
-      <c r="J5" s="114" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="114" t="s">
+      <c r="B5" s="107"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="122"/>
+      <c r="M5" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="115" t="s">
+      <c r="N5" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="116">
+    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="116" t="s">
+      <c r="E6" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="119">
-        <v>10</v>
-      </c>
-      <c r="G6" s="120" t="s">
-        <v>137</v>
-      </c>
-      <c r="H6" s="120" t="s">
-        <v>138</v>
-      </c>
-      <c r="I6" s="120" t="s">
-        <v>139</v>
-      </c>
-      <c r="J6" s="121" t="s">
-        <v>140</v>
-      </c>
-      <c r="K6" s="122" t="s">
-        <v>141</v>
-      </c>
-      <c r="L6" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="115">
+      <c r="F6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="29">
+        <v>2010</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="123" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="124" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="12">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="124" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="115" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="125">
-        <v>11</v>
-      </c>
-      <c r="G7" s="126" t="s">
+      <c r="F7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="126" t="s">
-        <v>144</v>
-      </c>
-      <c r="I7" s="126" t="s">
-        <v>139</v>
-      </c>
-      <c r="J7" s="127" t="s">
-        <v>145</v>
-      </c>
-      <c r="K7" s="128" t="s">
-        <v>146</v>
-      </c>
-      <c r="L7" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="115">
+      <c r="G7" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="8">
+        <v>2010</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="130" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="131"/>
+      <c r="M7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="12">
+        <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="123"/>
-      <c r="D8" s="124" t="s">
+      <c r="C8" s="105"/>
+      <c r="D8" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="115" t="s">
-        <v>110</v>
-      </c>
-      <c r="F8" s="125">
-        <v>12</v>
-      </c>
-      <c r="G8" s="126" t="s">
-        <v>147</v>
-      </c>
-      <c r="H8" s="126" t="s">
-        <v>148</v>
-      </c>
-      <c r="I8" s="126" t="s">
-        <v>149</v>
-      </c>
-      <c r="J8" s="127" t="s">
-        <v>150</v>
-      </c>
-      <c r="K8" s="129" t="s">
-        <v>141</v>
-      </c>
-      <c r="L8" s="116" t="s">
-        <v>142</v>
+      <c r="F8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="115">
+      <c r="B9" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="123"/>
-      <c r="D9" s="124" t="s">
+      <c r="C9" s="105"/>
+      <c r="D9" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="132" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="133"/>
+      <c r="M9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C10" s="105"/>
+      <c r="D10" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="115" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="125">
-        <v>13</v>
-      </c>
-      <c r="G9" s="126" t="s">
-        <v>151</v>
-      </c>
-      <c r="H9" s="126" t="s">
-        <v>152</v>
-      </c>
-      <c r="I9" s="126" t="s">
-        <v>153</v>
-      </c>
-      <c r="J9" s="127" t="s">
-        <v>154</v>
-      </c>
-      <c r="K9" s="128" t="s">
-        <v>155</v>
-      </c>
-      <c r="L9" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="115">
+      <c r="E10" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="11">
+        <v>2010</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="126"/>
+      <c r="M10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C11" s="105"/>
+      <c r="D11" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="11">
+        <v>2010</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="126"/>
+      <c r="M11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C12" s="105"/>
+      <c r="D12" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="11">
+        <v>2010</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="126"/>
+      <c r="M12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="25">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C13" s="106"/>
+      <c r="D13" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="119" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="120"/>
+      <c r="M13" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="98" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="99"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="98" t="s">
+        <v>120</v>
+      </c>
+      <c r="N17" s="99"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="101"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="112" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="113" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="96" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="114" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" s="115"/>
+      <c r="J18" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="L18" s="96" t="s">
+        <v>123</v>
+      </c>
+      <c r="M18" s="102" t="s">
+        <v>126</v>
+      </c>
+      <c r="N18" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="O18" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="P18" s="96" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="112"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="96"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="38">
+        <v>8</v>
+      </c>
+      <c r="D20" s="40">
         <v>5</v>
       </c>
-      <c r="C10" s="123"/>
-      <c r="D10" s="118" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="115">
-        <v>14</v>
-      </c>
-      <c r="G10" s="116" t="s">
-        <v>156</v>
-      </c>
-      <c r="H10" s="116" t="s">
-        <v>157</v>
-      </c>
-      <c r="I10" s="116" t="s">
-        <v>149</v>
-      </c>
-      <c r="J10" s="115" t="s">
-        <v>158</v>
-      </c>
-      <c r="K10" s="130" t="s">
-        <v>141</v>
-      </c>
-      <c r="L10" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="115">
-        <f>B10+1</f>
-        <v>6</v>
-      </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="118" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="131">
-        <v>15</v>
-      </c>
-      <c r="G11" s="131" t="s">
-        <v>160</v>
-      </c>
-      <c r="H11" s="131" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" s="131" t="s">
-        <v>162</v>
-      </c>
-      <c r="J11" s="131" t="s">
-        <v>163</v>
-      </c>
-      <c r="K11" s="128" t="s">
-        <v>155</v>
-      </c>
-      <c r="L11" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="115">
-        <f>B11+1</f>
-        <v>7</v>
-      </c>
-      <c r="C12" s="123"/>
-      <c r="D12" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="115" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" s="131">
-        <v>16</v>
-      </c>
-      <c r="G12" s="132" t="s">
-        <v>165</v>
-      </c>
-      <c r="H12" s="132" t="s">
-        <v>166</v>
-      </c>
-      <c r="I12" s="131" t="s">
-        <v>163</v>
-      </c>
-      <c r="J12" s="131" t="s">
-        <v>167</v>
-      </c>
-      <c r="K12" s="133" t="s">
-        <v>141</v>
-      </c>
-      <c r="L12" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="114">
-        <v>8</v>
-      </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="134" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="F13" s="135">
-        <v>17</v>
-      </c>
-      <c r="G13" s="136" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13" s="137" t="s">
-        <v>170</v>
-      </c>
-      <c r="I13" s="114" t="s">
-        <v>162</v>
-      </c>
-      <c r="J13" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="K13" s="138" t="s">
-        <v>155</v>
-      </c>
-      <c r="L13" s="116" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-    </row>
-    <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="5"/>
-    </row>
-    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="90" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="90" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" s="93"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="90" t="s">
-        <v>116</v>
-      </c>
-      <c r="N17" s="93"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="92"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="88" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="89" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="98" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="95"/>
-      <c r="J18" s="88" t="s">
-        <v>117</v>
-      </c>
-      <c r="K18" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L18" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="M18" s="99" t="s">
-        <v>122</v>
-      </c>
-      <c r="N18" s="88" t="s">
-        <v>117</v>
-      </c>
-      <c r="O18" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="P18" s="89" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="86"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="89"/>
-    </row>
-    <row r="20" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B20" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="25">
-        <v>8</v>
-      </c>
-      <c r="D20" s="27">
-        <v>7</v>
-      </c>
-      <c r="E20" s="27">
-        <v>1</v>
-      </c>
-      <c r="F20" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="101" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="I20" s="85"/>
+      <c r="E20" s="40">
+        <v>3</v>
+      </c>
+      <c r="F20" s="41"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="110" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="111"/>
       <c r="J20" s="2">
-        <v>8</v>
-      </c>
-      <c r="K20" s="27">
-        <v>8</v>
-      </c>
-      <c r="L20" s="28">
+        <v>3</v>
+      </c>
+      <c r="K20" s="40">
+        <v>3</v>
+      </c>
+      <c r="L20" s="41">
         <v>0</v>
       </c>
-      <c r="M20" s="32" t="s">
-        <v>123</v>
+      <c r="M20" s="45" t="s">
+        <v>127</v>
       </c>
       <c r="N20" s="2">
-        <v>8</v>
-      </c>
-      <c r="O20" s="27">
-        <v>8</v>
-      </c>
-      <c r="P20" s="28">
+        <v>5</v>
+      </c>
+      <c r="O20" s="40">
+        <v>5</v>
+      </c>
+      <c r="P20" s="41">
         <v>0</v>
       </c>
     </row>
@@ -4390,13 +4174,21 @@
       <c r="M21" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+  <mergeCells count="36">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
@@ -4413,18 +4205,13 @@
     <mergeCell ref="H18:I19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="K18:K19"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
   </mergeCells>
-  <conditionalFormatting sqref="F4:L4">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(F4))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4432,6 +4219,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4569,22 +4371,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4600,21 +4404,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>